--- a/biomed_inventory_app/app/data/inventory_master.xlsx
+++ b/biomed_inventory_app/app/data/inventory_master.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -806,7 +806,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -984,7 +984,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M153" t="inlineStr"/>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M168" t="inlineStr"/>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M176" t="inlineStr"/>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M180" t="inlineStr"/>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M183" t="inlineStr"/>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M186" t="inlineStr"/>
@@ -11574,7 +11574,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M187" t="inlineStr"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M191" t="inlineStr"/>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M193" t="inlineStr"/>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M196" t="inlineStr"/>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M197" t="inlineStr"/>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M198" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
@@ -12328,7 +12328,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M200" t="inlineStr"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M201" t="inlineStr"/>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M204" t="inlineStr"/>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M206" t="inlineStr"/>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
@@ -12792,7 +12792,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M208" t="inlineStr"/>
@@ -12850,7 +12850,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M210" t="inlineStr"/>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M212" t="inlineStr"/>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M214" t="inlineStr"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M217" t="inlineStr"/>
@@ -13372,7 +13372,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M218" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
@@ -13488,7 +13488,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M220" t="inlineStr"/>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M221" t="inlineStr"/>
@@ -13604,7 +13604,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M222" t="inlineStr"/>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M223" t="inlineStr"/>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M225" t="inlineStr"/>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M227" t="inlineStr"/>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M229" t="inlineStr"/>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M230" t="inlineStr"/>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M231" t="inlineStr"/>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M232" t="inlineStr"/>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M233" t="inlineStr"/>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M234" t="inlineStr"/>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M235" t="inlineStr"/>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M236" t="inlineStr"/>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M237" t="inlineStr"/>
@@ -14532,7 +14532,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M238" t="inlineStr"/>
@@ -14590,7 +14590,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M239" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M240" t="inlineStr"/>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M241" t="inlineStr"/>
@@ -14764,7 +14764,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M242" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M243" t="inlineStr"/>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M244" t="inlineStr"/>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M245" t="inlineStr"/>
@@ -14996,7 +14996,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M246" t="inlineStr"/>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M247" t="inlineStr"/>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M248" t="inlineStr"/>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M249" t="inlineStr"/>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M250" t="inlineStr"/>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M251" t="inlineStr"/>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M252" t="inlineStr"/>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M253" t="inlineStr"/>
@@ -15460,7 +15460,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M254" t="inlineStr"/>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M255" t="inlineStr"/>
@@ -15576,7 +15576,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M256" t="inlineStr"/>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M257" t="inlineStr"/>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M258" t="inlineStr"/>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M259" t="inlineStr"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M260" t="inlineStr"/>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M261" t="inlineStr"/>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M262" t="inlineStr"/>
@@ -15982,7 +15982,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M263" t="inlineStr"/>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M264" t="inlineStr"/>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
       <c r="M265" t="inlineStr"/>
@@ -16714,14 +16714,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>General Hospital</t>
+          <t>Central Hospital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Smith</t>
+          <t>Dr. Johnson</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -16749,12 +16749,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:12</t>
+          <t>2026-05-21T21:15:41</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:12</t>
+          <t>2026-05-21T21:15:41</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16776,7 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -16831,12 +16831,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Created CASE-260521-0001</t>
+          <t>Created unified case CASE-1779387341</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:12</t>
+          <t>2026-05-21T21:15:41</t>
         </is>
       </c>
     </row>
@@ -17095,13 +17095,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
   </cols>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CASE-260521-0001</t>
+          <t>CASE-1779387341</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -17172,17 +17172,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>General Hospital</t>
+          <t>Central Hospital</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Smith</t>
+          <t>Dr. Johnson</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -17192,17 +17192,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Patient monitoring system maintenance</t>
+          <t>Urgent equipment support</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:12</t>
+          <t>2026-05-21T21:15:41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:12</t>
+          <t>2026-05-21T21:15:41</t>
         </is>
       </c>
     </row>
@@ -17217,12 +17217,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -17417,10 +17417,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>not_ordered</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+          <t>po_draft</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>PO-1779387341</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
@@ -17431,12 +17435,88 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:12</t>
+          <t>2026-05-21T21:15:41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:12</t>
+          <t>2026-05-21T21:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Monitor Accessory</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>accessory</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>po_draft</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>PO-1779387341</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-05-21T21:15:41</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-05-21T21:15:41</t>
         </is>
       </c>
     </row>
@@ -28337,7 +28417,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28395,7 +28475,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28424,7 +28504,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28453,7 +28533,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28562,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28511,7 +28591,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28540,7 +28620,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28569,7 +28649,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28598,7 +28678,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28707,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28656,7 +28736,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28685,7 +28765,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28714,7 +28794,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28743,7 +28823,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28772,7 +28852,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28801,7 +28881,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28830,7 +28910,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28859,7 +28939,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28888,7 +28968,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28917,7 +28997,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28946,7 +29026,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -28975,7 +29055,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29004,7 +29084,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29033,7 +29113,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29062,7 +29142,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29171,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29120,7 +29200,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29149,7 +29229,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29178,7 +29258,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29207,7 +29287,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29236,7 +29316,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29265,7 +29345,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29374,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29323,7 +29403,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29352,7 +29432,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29381,7 +29461,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29410,7 +29490,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29439,7 +29519,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29468,7 +29548,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29497,7 +29577,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29526,7 +29606,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29555,7 +29635,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29584,7 +29664,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29613,7 +29693,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29642,7 +29722,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29671,7 +29751,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29700,7 +29780,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29729,7 +29809,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29758,7 +29838,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29787,7 +29867,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29816,7 +29896,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29845,7 +29925,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29874,7 +29954,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29903,7 +29983,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29932,7 +30012,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29961,7 +30041,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -29990,7 +30070,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30099,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30048,7 +30128,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30157,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30106,7 +30186,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30215,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30164,7 +30244,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30193,7 +30273,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30222,7 +30302,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30251,7 +30331,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30280,7 +30360,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30309,7 +30389,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30338,7 +30418,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30367,7 +30447,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30396,7 +30476,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30425,7 +30505,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30454,7 +30534,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30483,7 +30563,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30512,7 +30592,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30541,7 +30621,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30570,7 +30650,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30599,7 +30679,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30628,7 +30708,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30657,7 +30737,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30686,7 +30766,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30715,7 +30795,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30744,7 +30824,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30773,7 +30853,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30802,7 +30882,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30831,7 +30911,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30860,7 +30940,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30889,7 +30969,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30918,7 +30998,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30947,7 +31027,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -30976,7 +31056,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31005,7 +31085,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31034,7 +31114,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31063,7 +31143,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31092,7 +31172,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31121,7 +31201,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31150,7 +31230,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31179,7 +31259,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31208,7 +31288,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31237,7 +31317,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31266,7 +31346,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31295,7 +31375,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31324,7 +31404,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31353,7 +31433,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31382,7 +31462,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31411,7 +31491,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31520,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31469,7 +31549,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31578,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31527,7 +31607,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31556,7 +31636,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31585,7 +31665,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31614,7 +31694,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31643,7 +31723,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31672,7 +31752,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31701,7 +31781,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31730,7 +31810,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31759,7 +31839,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31788,7 +31868,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31817,7 +31897,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31926,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31875,7 +31955,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31984,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31933,7 +32013,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31962,7 +32042,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -31991,7 +32071,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32020,7 +32100,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32049,7 +32129,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32078,7 +32158,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32107,7 +32187,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32136,7 +32216,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32165,7 +32245,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32194,7 +32274,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32303,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32252,7 +32332,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32281,7 +32361,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32310,7 +32390,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32339,7 +32419,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32368,7 +32448,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32397,7 +32477,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32426,7 +32506,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32455,7 +32535,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32484,7 +32564,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32513,7 +32593,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32542,7 +32622,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32571,7 +32651,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32600,7 +32680,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32629,7 +32709,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32658,7 +32738,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32687,7 +32767,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32716,7 +32796,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32745,7 +32825,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32854,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32803,7 +32883,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32832,7 +32912,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32861,7 +32941,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32890,7 +32970,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32919,7 +32999,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32948,7 +33028,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -32977,7 +33057,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33006,7 +33086,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33035,7 +33115,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33064,7 +33144,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33093,7 +33173,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33122,7 +33202,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33151,7 +33231,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33180,7 +33260,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33209,7 +33289,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33238,7 +33318,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33267,7 +33347,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33296,7 +33376,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33325,7 +33405,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33434,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33463,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33412,7 +33492,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33441,7 +33521,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33470,7 +33550,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33499,7 +33579,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33528,7 +33608,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33557,7 +33637,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33586,7 +33666,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33615,7 +33695,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33644,7 +33724,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33673,7 +33753,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33702,7 +33782,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33731,7 +33811,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33760,7 +33840,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33789,7 +33869,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33818,7 +33898,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33847,7 +33927,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33876,7 +33956,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33905,7 +33985,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33934,7 +34014,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33963,7 +34043,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -33992,7 +34072,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34021,7 +34101,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34050,7 +34130,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34079,7 +34159,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34188,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34137,7 +34217,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34166,7 +34246,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34195,7 +34275,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34224,7 +34304,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34253,7 +34333,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34282,7 +34362,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34311,7 +34391,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34340,7 +34420,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34369,7 +34449,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34398,7 +34478,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34427,7 +34507,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34456,7 +34536,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34485,7 +34565,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34514,7 +34594,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34543,7 +34623,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34572,7 +34652,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34601,7 +34681,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34630,7 +34710,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34659,7 +34739,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34688,7 +34768,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34717,7 +34797,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34746,7 +34826,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34775,7 +34855,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34804,7 +34884,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34833,7 +34913,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34862,7 +34942,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34891,7 +34971,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34920,7 +35000,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34949,7 +35029,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -34978,7 +35058,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35087,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35036,7 +35116,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35065,7 +35145,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35094,7 +35174,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35123,7 +35203,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35152,7 +35232,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35181,7 +35261,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35210,7 +35290,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35239,7 +35319,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35268,7 +35348,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35297,7 +35377,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35326,7 +35406,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35355,7 +35435,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35384,7 +35464,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35493,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35442,7 +35522,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35471,7 +35551,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35500,7 +35580,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35529,7 +35609,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35558,7 +35638,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35587,7 +35667,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35616,7 +35696,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35645,7 +35725,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35674,7 +35754,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35703,7 +35783,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35732,7 +35812,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35761,7 +35841,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35790,7 +35870,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35819,7 +35899,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35848,7 +35928,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35877,7 +35957,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35906,7 +35986,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35935,7 +36015,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -35964,7 +36044,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-05-21T21:12:09</t>
+          <t>2026-05-21T21:15:37</t>
         </is>
       </c>
     </row>
@@ -36714,22 +36794,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36797,6 +36878,61 @@
         <is>
           <t>invoice_id</t>
         </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PO-1779387341</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>To be assigned</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Auto-generated for CASE-1779387341</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-21T21:15:41</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-05-21T21:15:41</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -36810,13 +36946,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -36824,8 +36960,8 @@
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
   </cols>
@@ -36907,6 +37043,96 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PO-1779387341</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ECG Cable</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-05-21T21:15:41</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-05-21T21:15:41</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PO-1779387341</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Monitor Accessory</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-05-21T21:15:41</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-05-21T21:15:41</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
